--- a/public/data/Russian_Similar_Words.xlsx
+++ b/public/data/Russian_Similar_Words.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew\public\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3536E9-2F13-42AD-AD6F-5B71986BAB62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72813139-5B77-432E-83F7-7B956BAEC558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9454,9 +9454,6 @@
     <t>мечта</t>
   </si>
   <si>
-    <t>מֵצִ'טָה</t>
-  </si>
-  <si>
     <t>חלום</t>
   </si>
   <si>
@@ -9658,6 +9655,9 @@
   </si>
   <si>
     <t>קָאלֵנְדָר</t>
+  </si>
+  <si>
+    <t>מֵצְ'טָה</t>
   </si>
 </sst>
 </file>
@@ -10079,15 +10079,15 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>3104</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>3105</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>3106</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B2" t="s">
         <v>2745</v>
@@ -10110,7 +10110,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B3" t="s">
         <v>2750</v>
@@ -10133,7 +10133,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B4" t="s">
         <v>2755</v>
@@ -10156,7 +10156,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B5" t="s">
         <v>2760</v>
@@ -10179,7 +10179,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
@@ -10199,7 +10199,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
@@ -10219,7 +10219,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -10239,7 +10239,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
@@ -10259,7 +10259,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B10" t="s">
         <v>18</v>
@@ -10279,7 +10279,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B11" t="s">
         <v>20</v>
@@ -10299,7 +10299,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B12" t="s">
         <v>22</v>
@@ -10319,7 +10319,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
@@ -10339,7 +10339,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B14" t="s">
         <v>28</v>
@@ -10359,7 +10359,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
@@ -10379,7 +10379,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -10399,7 +10399,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B18" t="s">
         <v>40</v>
@@ -10439,7 +10439,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B19" t="s">
         <v>44</v>
@@ -10459,7 +10459,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B20" t="s">
         <v>47</v>
@@ -10479,7 +10479,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B21" t="s">
         <v>50</v>
@@ -10499,7 +10499,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B22" t="s">
         <v>53</v>
@@ -10519,7 +10519,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B23" t="s">
         <v>57</v>
@@ -10539,7 +10539,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B24" t="s">
         <v>59</v>
@@ -10559,7 +10559,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B25" t="s">
         <v>62</v>
@@ -10579,7 +10579,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B26" t="s">
         <v>65</v>
@@ -10599,7 +10599,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B27" t="s">
         <v>69</v>
@@ -10619,7 +10619,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B28" t="s">
         <v>72</v>
@@ -10639,7 +10639,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B29" t="s">
         <v>75</v>
@@ -10659,7 +10659,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B30" t="s">
         <v>77</v>
@@ -10679,7 +10679,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B31" t="s">
         <v>80</v>
@@ -10699,7 +10699,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B32" t="s">
         <v>84</v>
@@ -10719,7 +10719,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B33" t="s">
         <v>88</v>
@@ -10739,7 +10739,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B34" t="s">
         <v>92</v>
@@ -10759,7 +10759,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B35" t="s">
         <v>96</v>
@@ -10779,7 +10779,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B36" t="s">
         <v>100</v>
@@ -10799,7 +10799,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B37" t="s">
         <v>104</v>
@@ -10819,7 +10819,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B38" t="s">
         <v>108</v>
@@ -10839,7 +10839,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B39" t="s">
         <v>111</v>
@@ -10859,7 +10859,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B40" t="s">
         <v>114</v>
@@ -10879,7 +10879,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B41" t="s">
         <v>118</v>
@@ -10899,7 +10899,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B42" t="s">
         <v>121</v>
@@ -10919,7 +10919,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B43" t="s">
         <v>124</v>
@@ -10939,7 +10939,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B44" t="s">
         <v>127</v>
@@ -10959,7 +10959,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B45" t="s">
         <v>130</v>
@@ -10979,7 +10979,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B46" t="s">
         <v>133</v>
@@ -10999,7 +10999,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B47" t="s">
         <v>136</v>
@@ -11019,7 +11019,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B48" t="s">
         <v>139</v>
@@ -11039,7 +11039,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B49" t="s">
         <v>142</v>
@@ -11059,7 +11059,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B50" t="s">
         <v>145</v>
@@ -11079,7 +11079,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B51" t="s">
         <v>149</v>
@@ -11099,7 +11099,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B52" t="s">
         <v>152</v>
@@ -11119,7 +11119,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B53" t="s">
         <v>154</v>
@@ -11139,7 +11139,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B54" t="s">
         <v>157</v>
@@ -11159,7 +11159,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B55" t="s">
         <v>159</v>
@@ -11179,7 +11179,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B56" t="s">
         <v>162</v>
@@ -11199,7 +11199,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B57" t="s">
         <v>165</v>
@@ -11219,7 +11219,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B58" t="s">
         <v>169</v>
@@ -11239,7 +11239,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B59" t="s">
         <v>173</v>
@@ -11259,7 +11259,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B60" t="s">
         <v>177</v>
@@ -11279,7 +11279,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B61" t="s">
         <v>180</v>
@@ -11299,7 +11299,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="B62" t="s">
         <v>184</v>
@@ -11319,7 +11319,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B63" t="s">
         <v>188</v>
@@ -11339,7 +11339,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B64" t="s">
         <v>191</v>
@@ -11359,7 +11359,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B65" t="s">
         <v>194</v>
@@ -11379,7 +11379,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B66" t="s">
         <v>198</v>
@@ -11399,7 +11399,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B67" t="s">
         <v>201</v>
@@ -11419,7 +11419,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B68" t="s">
         <v>203</v>
@@ -11439,7 +11439,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B69" t="s">
         <v>206</v>
@@ -11459,7 +11459,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B70" t="s">
         <v>210</v>
@@ -11479,7 +11479,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B71" t="s">
         <v>214</v>
@@ -11499,7 +11499,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B72" t="s">
         <v>218</v>
@@ -11519,7 +11519,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B73" t="s">
         <v>222</v>
@@ -11539,7 +11539,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B74" t="s">
         <v>226</v>
@@ -11559,7 +11559,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B75" t="s">
         <v>230</v>
@@ -11579,7 +11579,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B76" t="s">
         <v>233</v>
@@ -11599,7 +11599,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B77" t="s">
         <v>236</v>
@@ -11619,7 +11619,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B78" t="s">
         <v>240</v>
@@ -11639,7 +11639,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B79" t="s">
         <v>243</v>
@@ -11659,7 +11659,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B80" t="s">
         <v>247</v>
@@ -11679,7 +11679,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B81" t="s">
         <v>252</v>
@@ -11699,7 +11699,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B82" t="s">
         <v>255</v>
@@ -11719,7 +11719,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B83" t="s">
         <v>258</v>
@@ -11739,7 +11739,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B84" t="s">
         <v>261</v>
@@ -11759,7 +11759,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B85" t="s">
         <v>263</v>
@@ -11779,7 +11779,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="B86" t="s">
         <v>267</v>
@@ -11799,7 +11799,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B87" t="s">
         <v>271</v>
@@ -11819,7 +11819,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B88" t="s">
         <v>274</v>
@@ -11839,7 +11839,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B89" t="s">
         <v>277</v>
@@ -11859,7 +11859,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B90" t="s">
         <v>281</v>
@@ -11879,7 +11879,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B91" t="s">
         <v>285</v>
@@ -11899,7 +11899,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B92" t="s">
         <v>289</v>
@@ -11919,7 +11919,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B93" t="s">
         <v>292</v>
@@ -11939,7 +11939,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B94" t="s">
         <v>296</v>
@@ -11959,7 +11959,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B95" t="s">
         <v>299</v>
@@ -11979,7 +11979,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="B96" t="s">
         <v>303</v>
@@ -11999,7 +11999,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="B97" t="s">
         <v>306</v>
@@ -12019,7 +12019,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="B98" t="s">
         <v>309</v>
@@ -12039,7 +12039,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B99" t="s">
         <v>312</v>
@@ -12059,7 +12059,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B100" t="s">
         <v>316</v>
@@ -12079,7 +12079,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B101" t="s">
         <v>320</v>
@@ -12099,7 +12099,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B102" t="s">
         <v>323</v>
@@ -12119,7 +12119,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B103" t="s">
         <v>327</v>
@@ -12139,7 +12139,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B104" t="s">
         <v>330</v>
@@ -12159,7 +12159,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="B105" t="s">
         <v>332</v>
@@ -12179,7 +12179,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B106" t="s">
         <v>334</v>
@@ -12199,7 +12199,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B107" t="s">
         <v>338</v>
@@ -12219,7 +12219,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B108" t="s">
         <v>341</v>
@@ -12239,7 +12239,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B109" t="s">
         <v>345</v>
@@ -12259,7 +12259,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B110" t="s">
         <v>349</v>
@@ -12279,7 +12279,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B111" t="s">
         <v>352</v>
@@ -12299,7 +12299,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B112" t="s">
         <v>355</v>
@@ -12319,7 +12319,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B113" t="s">
         <v>359</v>
@@ -12339,7 +12339,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="B114" t="s">
         <v>363</v>
@@ -12359,13 +12359,13 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="B115" t="s">
         <v>366</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="D115" s="4" t="s">
         <v>367</v>
@@ -12379,7 +12379,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B116" t="s">
         <v>368</v>
@@ -12399,7 +12399,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B117" t="s">
         <v>372</v>
@@ -12419,7 +12419,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B118" t="s">
         <v>374</v>
@@ -12479,7 +12479,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B121" t="s">
         <v>384</v>
@@ -12499,7 +12499,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B122" t="s">
         <v>388</v>
@@ -12519,7 +12519,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B123" t="s">
         <v>392</v>
@@ -12539,7 +12539,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="B124" t="s">
         <v>395</v>
@@ -12559,7 +12559,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="B125" t="s">
         <v>398</v>
@@ -12579,7 +12579,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B126" t="s">
         <v>400</v>
@@ -12599,7 +12599,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B127" t="s">
         <v>404</v>
@@ -12619,7 +12619,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B128" t="s">
         <v>408</v>
@@ -12639,7 +12639,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B129" t="s">
         <v>411</v>
@@ -12659,7 +12659,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B130" t="s">
         <v>413</v>
@@ -12679,7 +12679,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B131" t="s">
         <v>416</v>
@@ -12699,7 +12699,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B132" t="s">
         <v>420</v>
@@ -12719,7 +12719,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B133" t="s">
         <v>423</v>
@@ -12739,7 +12739,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B134" t="s">
         <v>427</v>
@@ -12759,7 +12759,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B135" t="s">
         <v>430</v>
@@ -12779,7 +12779,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B136" t="s">
         <v>434</v>
@@ -12799,7 +12799,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="B137" t="s">
         <v>437</v>
@@ -12819,7 +12819,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="B138" t="s">
         <v>440</v>
@@ -12839,7 +12839,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B139" t="s">
         <v>444</v>
@@ -12859,7 +12859,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B140" t="s">
         <v>447</v>
@@ -12879,7 +12879,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="B141" t="s">
         <v>450</v>
@@ -12899,7 +12899,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="B142" t="s">
         <v>453</v>
@@ -12919,7 +12919,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B143" t="s">
         <v>455</v>
@@ -12939,7 +12939,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B144" t="s">
         <v>459</v>
@@ -12959,7 +12959,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B145" t="s">
         <v>462</v>
@@ -12979,7 +12979,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B146" t="s">
         <v>466</v>
@@ -12999,7 +12999,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B147" t="s">
         <v>468</v>
@@ -13019,7 +13019,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B148" t="s">
         <v>470</v>
@@ -13039,7 +13039,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B149" t="s">
         <v>473</v>
@@ -13059,7 +13059,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B150" t="s">
         <v>475</v>
@@ -13079,7 +13079,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B151" t="s">
         <v>478</v>
@@ -13099,7 +13099,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B152" t="s">
         <v>481</v>
@@ -13119,7 +13119,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B153" t="s">
         <v>483</v>
@@ -13139,7 +13139,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B154" t="s">
         <v>485</v>
@@ -13159,7 +13159,7 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B155" t="s">
         <v>488</v>
@@ -13179,7 +13179,7 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B156" t="s">
         <v>491</v>
@@ -13199,7 +13199,7 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B157" t="s">
         <v>494</v>
@@ -13219,7 +13219,7 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B158" t="s">
         <v>497</v>
@@ -13239,7 +13239,7 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B159" t="s">
         <v>501</v>
@@ -13259,7 +13259,7 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B160" t="s">
         <v>504</v>
@@ -13279,7 +13279,7 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B161" t="s">
         <v>508</v>
@@ -13299,7 +13299,7 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B162" t="s">
         <v>511</v>
@@ -13319,7 +13319,7 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B163" t="s">
         <v>515</v>
@@ -13339,7 +13339,7 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B164" t="s">
         <v>519</v>
@@ -13379,7 +13379,7 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B166" t="s">
         <v>526</v>
@@ -13399,7 +13399,7 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B167" t="s">
         <v>530</v>
@@ -13419,7 +13419,7 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="B168" t="s">
         <v>533</v>
@@ -13439,7 +13439,7 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B169" t="s">
         <v>536</v>
@@ -13459,7 +13459,7 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B170" t="s">
         <v>538</v>
@@ -13479,7 +13479,7 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B171" t="s">
         <v>542</v>
@@ -13499,7 +13499,7 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B172" t="s">
         <v>546</v>
@@ -13519,7 +13519,7 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B173" t="s">
         <v>550</v>
@@ -13539,7 +13539,7 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B174" t="s">
         <v>553</v>
@@ -13559,7 +13559,7 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="B175" t="s">
         <v>556</v>
@@ -13579,7 +13579,7 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="B176" t="s">
         <v>560</v>
@@ -13599,7 +13599,7 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B177" t="s">
         <v>564</v>
@@ -13619,7 +13619,7 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B178" t="s">
         <v>567</v>
@@ -13639,7 +13639,7 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B179" t="s">
         <v>571</v>
@@ -13659,7 +13659,7 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B180" t="s">
         <v>575</v>
@@ -13679,7 +13679,7 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B181" t="s">
         <v>578</v>
@@ -13699,13 +13699,13 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B182" t="s">
         <v>582</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="D182" s="4" t="s">
         <v>583</v>
@@ -13719,7 +13719,7 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B183" t="s">
         <v>585</v>
@@ -13739,7 +13739,7 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B184" t="s">
         <v>588</v>
@@ -13759,7 +13759,7 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="B185" t="s">
         <v>591</v>
@@ -13779,7 +13779,7 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B186" t="s">
         <v>595</v>
@@ -13799,7 +13799,7 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B187" t="s">
         <v>599</v>
@@ -13819,7 +13819,7 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B188" t="s">
         <v>601</v>
@@ -13839,7 +13839,7 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="B189" t="s">
         <v>604</v>
@@ -13859,7 +13859,7 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B190" t="s">
         <v>608</v>
@@ -13879,7 +13879,7 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="B191" t="s">
         <v>612</v>
@@ -13899,7 +13899,7 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B192" t="s">
         <v>616</v>
@@ -13919,7 +13919,7 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B193" t="s">
         <v>620</v>
@@ -13979,7 +13979,7 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="B196" t="s">
         <v>627</v>
@@ -13999,7 +13999,7 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="B197" t="s">
         <v>630</v>
@@ -14019,7 +14019,7 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B198" t="s">
         <v>633</v>
@@ -14039,7 +14039,7 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B199" t="s">
         <v>637</v>
@@ -14079,7 +14079,7 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B201" t="s">
         <v>643</v>
@@ -14119,7 +14119,7 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B203" t="s">
         <v>651</v>
@@ -14139,7 +14139,7 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B204" t="s">
         <v>654</v>
@@ -14159,7 +14159,7 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B205" t="s">
         <v>657</v>
@@ -14179,7 +14179,7 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B206" t="s">
         <v>661</v>
@@ -14199,7 +14199,7 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="B207" t="s">
         <v>665</v>
@@ -14219,7 +14219,7 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B208" t="s">
         <v>669</v>
@@ -14239,7 +14239,7 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B209" t="s">
         <v>673</v>
@@ -14259,7 +14259,7 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B210" t="s">
         <v>676</v>
@@ -14279,7 +14279,7 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B211" t="s">
         <v>679</v>
@@ -14299,7 +14299,7 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B212" t="s">
         <v>683</v>
@@ -14319,7 +14319,7 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B213" t="s">
         <v>686</v>
@@ -14339,7 +14339,7 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B214" t="s">
         <v>688</v>
@@ -14359,7 +14359,7 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B215" t="s">
         <v>691</v>
@@ -14379,7 +14379,7 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B216" t="s">
         <v>696</v>
@@ -14399,7 +14399,7 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B217" t="s">
         <v>700</v>
@@ -14419,7 +14419,7 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B218" t="s">
         <v>702</v>
@@ -14439,7 +14439,7 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B219" t="s">
         <v>705</v>
@@ -14459,7 +14459,7 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B220" t="s">
         <v>708</v>
@@ -14499,13 +14499,13 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B222" t="s">
         <v>714</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="D222" s="4" t="s">
         <v>715</v>
@@ -14519,7 +14519,7 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="B223" t="s">
         <v>717</v>
@@ -14539,7 +14539,7 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B224" t="s">
         <v>720</v>
@@ -14559,7 +14559,7 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B225" t="s">
         <v>724</v>
@@ -14579,7 +14579,7 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B226" t="s">
         <v>727</v>
@@ -14599,7 +14599,7 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B227" t="s">
         <v>730</v>
@@ -14619,7 +14619,7 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B228" t="s">
         <v>734</v>
@@ -14639,7 +14639,7 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B229" t="s">
         <v>736</v>
@@ -14659,7 +14659,7 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B230" t="s">
         <v>739</v>
@@ -14679,7 +14679,7 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B231" t="s">
         <v>743</v>
@@ -14699,7 +14699,7 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B232" t="s">
         <v>746</v>
@@ -14719,7 +14719,7 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B233" t="s">
         <v>750</v>
@@ -14739,7 +14739,7 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="B234" t="s">
         <v>754</v>
@@ -14759,7 +14759,7 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B235" t="s">
         <v>756</v>
@@ -14779,7 +14779,7 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B236" t="s">
         <v>760</v>
@@ -14799,7 +14799,7 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B237" t="s">
         <v>762</v>
@@ -14819,7 +14819,7 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="B238" t="s">
         <v>766</v>
@@ -14839,7 +14839,7 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B239" t="s">
         <v>770</v>
@@ -14859,7 +14859,7 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B240" t="s">
         <v>774</v>
@@ -14879,7 +14879,7 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B241" t="s">
         <v>777</v>
@@ -14899,7 +14899,7 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="B242" t="s">
         <v>781</v>
@@ -14919,7 +14919,7 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B243" t="s">
         <v>785</v>
@@ -14939,7 +14939,7 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="B244" t="s">
         <v>790</v>
@@ -14959,7 +14959,7 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B245" t="s">
         <v>793</v>
@@ -14979,7 +14979,7 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B246" t="s">
         <v>796</v>
@@ -14999,7 +14999,7 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B247" t="s">
         <v>799</v>
@@ -15019,7 +15019,7 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B248" t="s">
         <v>801</v>
@@ -15039,7 +15039,7 @@
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B249" t="s">
         <v>805</v>
@@ -15059,7 +15059,7 @@
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B250" t="s">
         <v>808</v>
@@ -15079,7 +15079,7 @@
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B251" t="s">
         <v>812</v>
@@ -15099,7 +15099,7 @@
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B252" t="s">
         <v>816</v>
@@ -15119,7 +15119,7 @@
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B253" t="s">
         <v>819</v>
@@ -15139,7 +15139,7 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="B254" t="s">
         <v>823</v>
@@ -15159,7 +15159,7 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B255" t="s">
         <v>827</v>
@@ -15179,7 +15179,7 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="B256" t="s">
         <v>830</v>
@@ -15199,7 +15199,7 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B257" t="s">
         <v>833</v>
@@ -15219,7 +15219,7 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B258" t="s">
         <v>837</v>
@@ -15239,7 +15239,7 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="B259" t="s">
         <v>840</v>
@@ -15259,7 +15259,7 @@
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B260" t="s">
         <v>842</v>
@@ -15279,7 +15279,7 @@
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B261" t="s">
         <v>845</v>
@@ -15299,7 +15299,7 @@
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B262" t="s">
         <v>849</v>
@@ -15319,7 +15319,7 @@
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B263" t="s">
         <v>852</v>
@@ -15339,7 +15339,7 @@
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B264" t="s">
         <v>855</v>
@@ -15359,7 +15359,7 @@
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B265" t="s">
         <v>858</v>
@@ -15379,7 +15379,7 @@
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B266" t="s">
         <v>861</v>
@@ -15399,7 +15399,7 @@
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B267" t="s">
         <v>863</v>
@@ -15419,7 +15419,7 @@
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B268" t="s">
         <v>865</v>
@@ -15439,7 +15439,7 @@
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B269" t="s">
         <v>869</v>
@@ -15459,7 +15459,7 @@
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="B270" t="s">
         <v>872</v>
@@ -15479,7 +15479,7 @@
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B271" t="s">
         <v>876</v>
@@ -15499,7 +15499,7 @@
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B272" t="s">
         <v>879</v>
@@ -15519,7 +15519,7 @@
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B273" t="s">
         <v>883</v>
@@ -15539,7 +15539,7 @@
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B274" t="s">
         <v>887</v>
@@ -15559,7 +15559,7 @@
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B275" t="s">
         <v>889</v>
@@ -15579,7 +15579,7 @@
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B276" t="s">
         <v>891</v>
@@ -15599,7 +15599,7 @@
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B277" t="s">
         <v>894</v>
@@ -15619,7 +15619,7 @@
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B278" t="s">
         <v>898</v>
@@ -15637,12 +15637,12 @@
         <v>-1</v>
       </c>
       <c r="L278" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="B279" t="s">
         <v>900</v>
@@ -15662,7 +15662,7 @@
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B280" t="s">
         <v>902</v>
@@ -15682,7 +15682,7 @@
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B281" t="s">
         <v>905</v>
@@ -15702,7 +15702,7 @@
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B282" t="s">
         <v>909</v>
@@ -15722,7 +15722,7 @@
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B283" t="s">
         <v>912</v>
@@ -15742,7 +15742,7 @@
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B284" t="s">
         <v>915</v>
@@ -15762,7 +15762,7 @@
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B285" t="s">
         <v>918</v>
@@ -15782,7 +15782,7 @@
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B286" t="s">
         <v>921</v>
@@ -15802,7 +15802,7 @@
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="B287" t="s">
         <v>924</v>
@@ -15822,7 +15822,7 @@
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B288" t="s">
         <v>926</v>
@@ -15842,7 +15842,7 @@
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B289" t="s">
         <v>929</v>
@@ -15862,7 +15862,7 @@
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B290" t="s">
         <v>932</v>
@@ -15882,7 +15882,7 @@
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B291" t="s">
         <v>935</v>
@@ -15902,7 +15902,7 @@
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="B292" t="s">
         <v>938</v>
@@ -15922,7 +15922,7 @@
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B293" t="s">
         <v>941</v>
@@ -15942,7 +15942,7 @@
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="B294" t="s">
         <v>944</v>
@@ -15982,7 +15982,7 @@
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B296" t="s">
         <v>950</v>
@@ -16002,7 +16002,7 @@
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B297" t="s">
         <v>954</v>
@@ -16022,7 +16022,7 @@
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="B298" t="s">
         <v>958</v>
@@ -16042,7 +16042,7 @@
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B299" t="s">
         <v>962</v>
@@ -16062,7 +16062,7 @@
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B300" t="s">
         <v>965</v>
@@ -16082,7 +16082,7 @@
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B301" t="s">
         <v>967</v>
@@ -16102,7 +16102,7 @@
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B302" t="s">
         <v>971</v>
@@ -16122,7 +16122,7 @@
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B303" t="s">
         <v>975</v>
@@ -16142,7 +16142,7 @@
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B304" t="s">
         <v>979</v>
@@ -16162,7 +16162,7 @@
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B305" t="s">
         <v>981</v>
@@ -16182,7 +16182,7 @@
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B306" t="s">
         <v>985</v>
@@ -16202,7 +16202,7 @@
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B307" t="s">
         <v>989</v>
@@ -16222,7 +16222,7 @@
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B308" t="s">
         <v>992</v>
@@ -16242,7 +16242,7 @@
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B309" t="s">
         <v>996</v>
@@ -16262,7 +16262,7 @@
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="B310" t="s">
         <v>1000</v>
@@ -16282,7 +16282,7 @@
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B311" t="s">
         <v>1003</v>
@@ -16302,7 +16302,7 @@
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B312" t="s">
         <v>1007</v>
@@ -16322,7 +16322,7 @@
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B313" t="s">
         <v>1011</v>
@@ -16342,7 +16342,7 @@
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B314" t="s">
         <v>1015</v>
@@ -16362,7 +16362,7 @@
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B315" t="s">
         <v>1018</v>
@@ -16382,7 +16382,7 @@
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B316" t="s">
         <v>1021</v>
@@ -16402,7 +16402,7 @@
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B317" t="s">
         <v>1025</v>
@@ -16422,7 +16422,7 @@
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B318" t="s">
         <v>1028</v>
@@ -16442,7 +16442,7 @@
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B319" t="s">
         <v>1031</v>
@@ -16462,7 +16462,7 @@
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B320" t="s">
         <v>1035</v>
@@ -16482,7 +16482,7 @@
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B321" t="s">
         <v>1039</v>
@@ -16502,7 +16502,7 @@
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B322" t="s">
         <v>1043</v>
@@ -16522,7 +16522,7 @@
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B323" t="s">
         <v>1046</v>
@@ -16542,7 +16542,7 @@
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B324" t="s">
         <v>1050</v>
@@ -16562,7 +16562,7 @@
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B325" t="s">
         <v>1053</v>
@@ -16582,7 +16582,7 @@
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B326" t="s">
         <v>1057</v>
@@ -16602,7 +16602,7 @@
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B327" t="s">
         <v>1061</v>
@@ -16622,7 +16622,7 @@
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B328" t="s">
         <v>1064</v>
@@ -16642,7 +16642,7 @@
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B329" t="s">
         <v>1067</v>
@@ -16662,7 +16662,7 @@
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B330" t="s">
         <v>1069</v>
@@ -16682,7 +16682,7 @@
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B331" t="s">
         <v>1072</v>
@@ -16702,7 +16702,7 @@
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B332" t="s">
         <v>1075</v>
@@ -16722,7 +16722,7 @@
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B333" t="s">
         <v>1078</v>
@@ -16742,7 +16742,7 @@
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B334" t="s">
         <v>1081</v>
@@ -16762,7 +16762,7 @@
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B335" t="s">
         <v>1084</v>
@@ -16782,7 +16782,7 @@
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B336" t="s">
         <v>1087</v>
@@ -16802,7 +16802,7 @@
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B337" t="s">
         <v>1090</v>
@@ -16822,7 +16822,7 @@
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B338" t="s">
         <v>1093</v>
@@ -16842,7 +16842,7 @@
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="B339" t="s">
         <v>1095</v>
@@ -16862,7 +16862,7 @@
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="B340" t="s">
         <v>1098</v>
@@ -16882,7 +16882,7 @@
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B341" t="s">
         <v>1100</v>
@@ -16902,7 +16902,7 @@
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B342" t="s">
         <v>1102</v>
@@ -16922,7 +16922,7 @@
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="B343" t="s">
         <v>1105</v>
@@ -16942,7 +16942,7 @@
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B344" t="s">
         <v>1108</v>
@@ -16962,7 +16962,7 @@
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B345" t="s">
         <v>1111</v>
@@ -16982,7 +16982,7 @@
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="B346" t="s">
         <v>1114</v>
@@ -17002,7 +17002,7 @@
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B347" t="s">
         <v>1117</v>
@@ -17022,7 +17022,7 @@
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B348" t="s">
         <v>1120</v>
@@ -17042,7 +17042,7 @@
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="B349" t="s">
         <v>1123</v>
@@ -17062,7 +17062,7 @@
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B350" t="s">
         <v>1126</v>
@@ -17082,7 +17082,7 @@
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="B351" t="s">
         <v>1129</v>
@@ -17102,7 +17102,7 @@
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B352" t="s">
         <v>1132</v>
@@ -17122,7 +17122,7 @@
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B353" t="s">
         <v>1135</v>
@@ -17142,7 +17142,7 @@
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B354" t="s">
         <v>1137</v>
@@ -17162,7 +17162,7 @@
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B355" t="s">
         <v>1140</v>
@@ -17182,7 +17182,7 @@
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B356" t="s">
         <v>1142</v>
@@ -17302,7 +17302,7 @@
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B362" t="s">
         <v>1157</v>
@@ -17322,7 +17322,7 @@
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B363" t="s">
         <v>1160</v>
@@ -17342,7 +17342,7 @@
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B364" t="s">
         <v>1162</v>
@@ -17362,7 +17362,7 @@
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B365" t="s">
         <v>1165</v>
@@ -17402,7 +17402,7 @@
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B367" t="s">
         <v>1170</v>
@@ -17442,7 +17442,7 @@
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="B369" t="s">
         <v>1175</v>
@@ -17462,7 +17462,7 @@
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B370" t="s">
         <v>1178</v>
@@ -17482,7 +17482,7 @@
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B371" t="s">
         <v>1181</v>
@@ -17502,7 +17502,7 @@
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B372" t="s">
         <v>1183</v>
@@ -17522,7 +17522,7 @@
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B373" t="s">
         <v>1185</v>
@@ -17542,7 +17542,7 @@
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B374" t="s">
         <v>1188</v>
@@ -17562,7 +17562,7 @@
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B375" t="s">
         <v>1190</v>
@@ -17582,7 +17582,7 @@
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B376" t="s">
         <v>1193</v>
@@ -17602,7 +17602,7 @@
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B377" t="s">
         <v>1195</v>
@@ -17622,7 +17622,7 @@
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B378" t="s">
         <v>1198</v>
@@ -17642,7 +17642,7 @@
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="B379" t="s">
         <v>1245</v>
@@ -17662,7 +17662,7 @@
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B380" t="s">
         <v>1248</v>
@@ -17682,7 +17682,7 @@
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B381" t="s">
         <v>1336</v>
@@ -17705,7 +17705,7 @@
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B382" t="s">
         <v>1341</v>
@@ -17728,7 +17728,7 @@
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B383" t="s">
         <v>1346</v>
@@ -17751,7 +17751,7 @@
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B384" t="s">
         <v>1351</v>
@@ -17774,7 +17774,7 @@
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B385" t="s">
         <v>1356</v>
@@ -17797,7 +17797,7 @@
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B386" t="s">
         <v>1361</v>
@@ -17820,7 +17820,7 @@
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B387" t="s">
         <v>1366</v>
@@ -17843,7 +17843,7 @@
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B388" t="s">
         <v>1371</v>
@@ -17866,7 +17866,7 @@
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B389" t="s">
         <v>1375</v>
@@ -17889,7 +17889,7 @@
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B390" t="s">
         <v>1380</v>
@@ -17912,7 +17912,7 @@
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B391" t="s">
         <v>1384</v>
@@ -17935,7 +17935,7 @@
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B392" t="s">
         <v>1389</v>
@@ -17958,7 +17958,7 @@
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B393" t="s">
         <v>1394</v>
@@ -17981,7 +17981,7 @@
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B394" t="s">
         <v>1399</v>
@@ -18004,7 +18004,7 @@
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B395" t="s">
         <v>1404</v>
@@ -18027,7 +18027,7 @@
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B396" t="s">
         <v>1409</v>
@@ -18050,7 +18050,7 @@
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B397" t="s">
         <v>1414</v>
@@ -18073,7 +18073,7 @@
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B398" t="s">
         <v>1419</v>
@@ -18096,7 +18096,7 @@
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B399" t="s">
         <v>1424</v>
@@ -18119,7 +18119,7 @@
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B400" t="s">
         <v>1429</v>
@@ -18142,7 +18142,7 @@
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B401" t="s">
         <v>1434</v>
@@ -18165,7 +18165,7 @@
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B402" t="s">
         <v>1439</v>
@@ -18188,7 +18188,7 @@
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B403" t="s">
         <v>1444</v>
@@ -18211,7 +18211,7 @@
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B404" t="s">
         <v>1449</v>
@@ -18234,7 +18234,7 @@
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B405" t="s">
         <v>1454</v>
@@ -18257,7 +18257,7 @@
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B406" t="s">
         <v>1459</v>
@@ -18280,7 +18280,7 @@
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B407" t="s">
         <v>1464</v>
@@ -18303,7 +18303,7 @@
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B408" t="s">
         <v>1469</v>
@@ -18326,7 +18326,7 @@
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B409" t="s">
         <v>1474</v>
@@ -18349,7 +18349,7 @@
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B410" t="s">
         <v>1479</v>
@@ -18372,7 +18372,7 @@
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B411" t="s">
         <v>1484</v>
@@ -18395,7 +18395,7 @@
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B412" t="s">
         <v>1489</v>
@@ -18418,7 +18418,7 @@
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B413" t="s">
         <v>1494</v>
@@ -18441,7 +18441,7 @@
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B414" t="s">
         <v>1499</v>
@@ -18464,7 +18464,7 @@
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B415" t="s">
         <v>1504</v>
@@ -18487,7 +18487,7 @@
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B416" t="s">
         <v>1509</v>
@@ -18510,7 +18510,7 @@
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B417" t="s">
         <v>1513</v>
@@ -18533,7 +18533,7 @@
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B418" t="s">
         <v>1518</v>
@@ -18556,7 +18556,7 @@
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B419" t="s">
         <v>1522</v>
@@ -18579,7 +18579,7 @@
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B420" t="s">
         <v>1527</v>
@@ -18602,7 +18602,7 @@
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B421" t="s">
         <v>1532</v>
@@ -18625,7 +18625,7 @@
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B422" t="s">
         <v>1537</v>
@@ -18648,7 +18648,7 @@
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B423" t="s">
         <v>1542</v>
@@ -18671,7 +18671,7 @@
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B424" t="s">
         <v>1547</v>
@@ -18694,7 +18694,7 @@
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B425" t="s">
         <v>1552</v>
@@ -18717,7 +18717,7 @@
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B426" t="s">
         <v>1557</v>
@@ -18740,7 +18740,7 @@
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B427" t="s">
         <v>1562</v>
@@ -18763,7 +18763,7 @@
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B428" t="s">
         <v>1567</v>
@@ -18786,7 +18786,7 @@
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B429" t="s">
         <v>1572</v>
@@ -18809,7 +18809,7 @@
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B430" t="s">
         <v>1577</v>
@@ -18832,7 +18832,7 @@
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B431" t="s">
         <v>1582</v>
@@ -18855,7 +18855,7 @@
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B432" t="s">
         <v>1587</v>
@@ -18878,7 +18878,7 @@
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B433" t="s">
         <v>1592</v>
@@ -18901,7 +18901,7 @@
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B434" t="s">
         <v>1597</v>
@@ -18924,7 +18924,7 @@
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B435" t="s">
         <v>1602</v>
@@ -18947,7 +18947,7 @@
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B436" t="s">
         <v>1607</v>
@@ -18970,7 +18970,7 @@
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B437" t="s">
         <v>1612</v>
@@ -18993,7 +18993,7 @@
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B438" t="s">
         <v>1617</v>
@@ -19016,7 +19016,7 @@
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B439" t="s">
         <v>1622</v>
@@ -19039,7 +19039,7 @@
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B440" t="s">
         <v>1627</v>
@@ -19062,7 +19062,7 @@
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B441" t="s">
         <v>1632</v>
@@ -19085,7 +19085,7 @@
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B442" t="s">
         <v>1637</v>
@@ -19108,7 +19108,7 @@
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B443" t="s">
         <v>1642</v>
@@ -19131,7 +19131,7 @@
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B444" t="s">
         <v>1647</v>
@@ -19154,7 +19154,7 @@
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B445" t="s">
         <v>1651</v>
@@ -19177,7 +19177,7 @@
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B446" t="s">
         <v>1656</v>
@@ -19200,7 +19200,7 @@
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B447" t="s">
         <v>1661</v>
@@ -19223,7 +19223,7 @@
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B448" t="s">
         <v>1666</v>
@@ -19246,7 +19246,7 @@
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B449" t="s">
         <v>1671</v>
@@ -19269,7 +19269,7 @@
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B450" t="s">
         <v>1676</v>
@@ -19292,7 +19292,7 @@
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B451" t="s">
         <v>1681</v>
@@ -19315,7 +19315,7 @@
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B452" t="s">
         <v>1686</v>
@@ -19338,7 +19338,7 @@
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B453" t="s">
         <v>1691</v>
@@ -19361,7 +19361,7 @@
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B454" t="s">
         <v>1696</v>
@@ -19384,7 +19384,7 @@
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B455" t="s">
         <v>1701</v>
@@ -19407,7 +19407,7 @@
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B456" t="s">
         <v>1706</v>
@@ -19430,7 +19430,7 @@
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B457" t="s">
         <v>1711</v>
@@ -19453,7 +19453,7 @@
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B458" t="s">
         <v>1716</v>
@@ -19476,7 +19476,7 @@
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B459" t="s">
         <v>1721</v>
@@ -19499,7 +19499,7 @@
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B460" t="s">
         <v>1726</v>
@@ -19522,7 +19522,7 @@
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B461" t="s">
         <v>1731</v>
@@ -19545,7 +19545,7 @@
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B462" t="s">
         <v>1736</v>
@@ -19568,7 +19568,7 @@
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B463" t="s">
         <v>1741</v>
@@ -19591,7 +19591,7 @@
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B464" t="s">
         <v>1746</v>
@@ -19614,7 +19614,7 @@
     </row>
     <row r="465" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B465" t="s">
         <v>1750</v>
@@ -19637,7 +19637,7 @@
     </row>
     <row r="466" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B466" t="s">
         <v>1755</v>
@@ -19660,7 +19660,7 @@
     </row>
     <row r="467" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B467" t="s">
         <v>1760</v>
@@ -19683,7 +19683,7 @@
     </row>
     <row r="468" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B468" t="s">
         <v>1765</v>
@@ -19706,7 +19706,7 @@
     </row>
     <row r="469" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B469" t="s">
         <v>1770</v>
@@ -19729,7 +19729,7 @@
     </row>
     <row r="470" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B470" t="s">
         <v>1775</v>
@@ -19752,7 +19752,7 @@
     </row>
     <row r="471" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B471" t="s">
         <v>1780</v>
@@ -19775,7 +19775,7 @@
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B472" t="s">
         <v>1785</v>
@@ -19798,7 +19798,7 @@
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B473" t="s">
         <v>1790</v>
@@ -19821,7 +19821,7 @@
     </row>
     <row r="474" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B474" t="s">
         <v>1795</v>
@@ -19844,7 +19844,7 @@
     </row>
     <row r="475" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B475" t="s">
         <v>1800</v>
@@ -19867,7 +19867,7 @@
     </row>
     <row r="476" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B476" t="s">
         <v>1805</v>
@@ -19890,7 +19890,7 @@
     </row>
     <row r="477" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B477" t="s">
         <v>1810</v>
@@ -19913,7 +19913,7 @@
     </row>
     <row r="478" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B478" t="s">
         <v>1815</v>
@@ -19936,7 +19936,7 @@
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B479" t="s">
         <v>1820</v>
@@ -19959,7 +19959,7 @@
     </row>
     <row r="480" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B480" t="s">
         <v>1825</v>
@@ -19982,7 +19982,7 @@
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B481" t="s">
         <v>1830</v>
@@ -20005,7 +20005,7 @@
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B482" t="s">
         <v>1835</v>
@@ -20028,7 +20028,7 @@
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B483" t="s">
         <v>1840</v>
@@ -20051,7 +20051,7 @@
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B484" t="s">
         <v>1845</v>
@@ -20074,7 +20074,7 @@
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B485" t="s">
         <v>1850</v>
@@ -20097,7 +20097,7 @@
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B486" t="s">
         <v>1855</v>
@@ -20120,7 +20120,7 @@
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B487" t="s">
         <v>1860</v>
@@ -20143,7 +20143,7 @@
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B488" t="s">
         <v>1865</v>
@@ -20166,7 +20166,7 @@
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B489" t="s">
         <v>1870</v>
@@ -20189,7 +20189,7 @@
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B490" t="s">
         <v>1875</v>
@@ -20212,7 +20212,7 @@
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B491" t="s">
         <v>1879</v>
@@ -20235,7 +20235,7 @@
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B492" t="s">
         <v>1884</v>
@@ -20258,7 +20258,7 @@
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B493" t="s">
         <v>1889</v>
@@ -20281,7 +20281,7 @@
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B494" t="s">
         <v>1894</v>
@@ -20304,7 +20304,7 @@
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B495" t="s">
         <v>1898</v>
@@ -20327,7 +20327,7 @@
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B496" t="s">
         <v>1903</v>
@@ -20350,7 +20350,7 @@
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B497" t="s">
         <v>1907</v>
@@ -20373,7 +20373,7 @@
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B498" t="s">
         <v>1912</v>
@@ -20396,7 +20396,7 @@
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B499" t="s">
         <v>1917</v>
@@ -20419,7 +20419,7 @@
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B500" t="s">
         <v>1921</v>
@@ -20442,7 +20442,7 @@
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B501" t="s">
         <v>1926</v>
@@ -20465,7 +20465,7 @@
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B502" t="s">
         <v>1931</v>
@@ -20488,7 +20488,7 @@
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B503" t="s">
         <v>1936</v>
@@ -20511,7 +20511,7 @@
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B504" t="s">
         <v>1941</v>
@@ -20534,7 +20534,7 @@
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B505" t="s">
         <v>1945</v>
@@ -20557,7 +20557,7 @@
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B506" t="s">
         <v>1950</v>
@@ -20580,7 +20580,7 @@
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B507" t="s">
         <v>1955</v>
@@ -20603,7 +20603,7 @@
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B508" t="s">
         <v>1960</v>
@@ -20626,7 +20626,7 @@
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B509" t="s">
         <v>1965</v>
@@ -20649,7 +20649,7 @@
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B510" t="s">
         <v>1970</v>
@@ -20672,7 +20672,7 @@
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B511" t="s">
         <v>1975</v>
@@ -20692,7 +20692,7 @@
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B512" t="s">
         <v>1979</v>
@@ -20715,7 +20715,7 @@
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B513" t="s">
         <v>1983</v>
@@ -20738,7 +20738,7 @@
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B514" t="s">
         <v>1988</v>
@@ -20761,7 +20761,7 @@
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B515" t="s">
         <v>1993</v>
@@ -20778,7 +20778,7 @@
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B516" t="s">
         <v>1996</v>
@@ -20795,7 +20795,7 @@
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B517" t="s">
         <v>1999</v>
@@ -20812,7 +20812,7 @@
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B518" t="s">
         <v>2002</v>
@@ -20835,7 +20835,7 @@
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B519" t="s">
         <v>2007</v>
@@ -20858,7 +20858,7 @@
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B520" t="s">
         <v>2012</v>
@@ -20875,7 +20875,7 @@
     </row>
     <row r="521" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B521" t="s">
         <v>2015</v>
@@ -20892,7 +20892,7 @@
     </row>
     <row r="522" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B522" t="s">
         <v>2018</v>
@@ -20909,7 +20909,7 @@
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B523" t="s">
         <v>2021</v>
@@ -20926,7 +20926,7 @@
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B524" t="s">
         <v>2024</v>
@@ -20943,7 +20943,7 @@
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B525" t="s">
         <v>2027</v>
@@ -20960,7 +20960,7 @@
     </row>
     <row r="526" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B526" t="s">
         <v>2030</v>
@@ -20977,7 +20977,7 @@
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B527" t="s">
         <v>2033</v>
@@ -21000,7 +21000,7 @@
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B528" t="s">
         <v>2038</v>
@@ -21023,7 +21023,7 @@
     </row>
     <row r="529" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B529" t="s">
         <v>2043</v>
@@ -21040,7 +21040,7 @@
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B530" t="s">
         <v>2046</v>
@@ -21057,7 +21057,7 @@
     </row>
     <row r="531" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B531" t="s">
         <v>2049</v>
@@ -21074,7 +21074,7 @@
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B532" t="s">
         <v>2052</v>
@@ -21091,7 +21091,7 @@
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B533" t="s">
         <v>2055</v>
@@ -21108,7 +21108,7 @@
     </row>
     <row r="534" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B534" t="s">
         <v>2058</v>
@@ -21125,7 +21125,7 @@
     </row>
     <row r="535" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B535" t="s">
         <v>2061</v>
@@ -21142,7 +21142,7 @@
     </row>
     <row r="536" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B536" t="s">
         <v>2064</v>
@@ -21159,7 +21159,7 @@
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B537" t="s">
         <v>2067</v>
@@ -21182,7 +21182,7 @@
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B538" t="s">
         <v>2072</v>
@@ -21205,7 +21205,7 @@
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B539" t="s">
         <v>2077</v>
@@ -21222,7 +21222,7 @@
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B540" t="s">
         <v>2080</v>
@@ -21239,7 +21239,7 @@
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B541" t="s">
         <v>2083</v>
@@ -21256,7 +21256,7 @@
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B542" t="s">
         <v>2086</v>
@@ -21273,7 +21273,7 @@
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B543" t="s">
         <v>2089</v>
@@ -21290,7 +21290,7 @@
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B544" t="s">
         <v>2092</v>
@@ -21307,7 +21307,7 @@
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B545" t="s">
         <v>2095</v>
@@ -21324,7 +21324,7 @@
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B546" t="s">
         <v>2098</v>
@@ -21341,7 +21341,7 @@
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B547" t="s">
         <v>2101</v>
@@ -21358,7 +21358,7 @@
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B548" t="s">
         <v>2104</v>
@@ -21375,7 +21375,7 @@
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B549" t="s">
         <v>2107</v>
@@ -21392,7 +21392,7 @@
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B550" t="s">
         <v>2110</v>
@@ -21409,7 +21409,7 @@
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B551" t="s">
         <v>2113</v>
@@ -21426,7 +21426,7 @@
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B552" t="s">
         <v>2116</v>
@@ -21443,7 +21443,7 @@
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B553" t="s">
         <v>2119</v>
@@ -21460,7 +21460,7 @@
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B554" t="s">
         <v>2122</v>
@@ -21477,7 +21477,7 @@
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B555" t="s">
         <v>2124</v>
@@ -21494,7 +21494,7 @@
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B556" t="s">
         <v>2049</v>
@@ -21511,7 +21511,7 @@
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B557" t="s">
         <v>2129</v>
@@ -21528,7 +21528,7 @@
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B558" t="s">
         <v>1921</v>
@@ -21545,7 +21545,7 @@
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B559" t="s">
         <v>2133</v>
@@ -21562,7 +21562,7 @@
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B560" t="s">
         <v>2002</v>
@@ -21579,7 +21579,7 @@
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B561" t="s">
         <v>2136</v>
@@ -21596,7 +21596,7 @@
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B562" t="s">
         <v>2138</v>
@@ -21613,7 +21613,7 @@
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B563" t="s">
         <v>2141</v>
@@ -21636,7 +21636,7 @@
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B564" t="s">
         <v>2146</v>
@@ -21659,7 +21659,7 @@
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B565" t="s">
         <v>2151</v>
@@ -21682,7 +21682,7 @@
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B566" t="s">
         <v>2156</v>
@@ -21705,7 +21705,7 @@
     </row>
     <row r="567" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B567" t="s">
         <v>2161</v>
@@ -21722,7 +21722,7 @@
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B568" t="s">
         <v>2164</v>
@@ -21739,7 +21739,7 @@
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B569" t="s">
         <v>2167</v>
@@ -21762,7 +21762,7 @@
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B570" t="s">
         <v>2172</v>
@@ -21785,7 +21785,7 @@
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B571" t="s">
         <v>2177</v>
@@ -21808,7 +21808,7 @@
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B572" t="s">
         <v>2182</v>
@@ -21831,7 +21831,7 @@
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B573" t="s">
         <v>2187</v>
@@ -21854,7 +21854,7 @@
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B574" t="s">
         <v>2192</v>
@@ -21877,7 +21877,7 @@
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B575" t="s">
         <v>2196</v>
@@ -21900,7 +21900,7 @@
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B576" t="s">
         <v>2200</v>
@@ -21923,7 +21923,7 @@
     </row>
     <row r="577" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B577" t="s">
         <v>2205</v>
@@ -21940,7 +21940,7 @@
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B578" t="s">
         <v>2208</v>
@@ -21957,7 +21957,7 @@
     </row>
     <row r="579" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B579" t="s">
         <v>2211</v>
@@ -21974,7 +21974,7 @@
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B580" t="s">
         <v>2214</v>
@@ -21997,7 +21997,7 @@
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B581" t="s">
         <v>2219</v>
@@ -22014,7 +22014,7 @@
     </row>
     <row r="582" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B582" t="s">
         <v>2222</v>
@@ -22031,7 +22031,7 @@
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B583" t="s">
         <v>2225</v>
@@ -22048,7 +22048,7 @@
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B584" t="s">
         <v>2228</v>
@@ -22065,7 +22065,7 @@
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B585" t="s">
         <v>2231</v>
@@ -22088,7 +22088,7 @@
     </row>
     <row r="586" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B586" t="s">
         <v>2236</v>
@@ -22111,7 +22111,7 @@
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B587" t="s">
         <v>2241</v>
@@ -22134,7 +22134,7 @@
     </row>
     <row r="588" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B588" t="s">
         <v>2246</v>
@@ -22157,7 +22157,7 @@
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B589" t="s">
         <v>2251</v>
@@ -22174,7 +22174,7 @@
     </row>
     <row r="590" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B590" t="s">
         <v>2254</v>
@@ -22197,7 +22197,7 @@
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B591" t="s">
         <v>2259</v>
@@ -22220,7 +22220,7 @@
     </row>
     <row r="592" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B592" t="s">
         <v>2264</v>
@@ -22243,7 +22243,7 @@
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B593" t="s">
         <v>2269</v>
@@ -22260,7 +22260,7 @@
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B594" t="s">
         <v>2272</v>
@@ -22283,7 +22283,7 @@
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B595" t="s">
         <v>2277</v>
@@ -22306,7 +22306,7 @@
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B596" t="s">
         <v>2282</v>
@@ -22329,7 +22329,7 @@
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B597" t="s">
         <v>2287</v>
@@ -22352,7 +22352,7 @@
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B598" t="s">
         <v>2292</v>
@@ -22375,7 +22375,7 @@
     </row>
     <row r="599" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B599" t="s">
         <v>2297</v>
@@ -22398,7 +22398,7 @@
     </row>
     <row r="600" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B600" t="s">
         <v>2302</v>
@@ -22421,7 +22421,7 @@
     </row>
     <row r="601" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B601" t="s">
         <v>2307</v>
@@ -22444,7 +22444,7 @@
     </row>
     <row r="602" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B602" t="s">
         <v>2312</v>
@@ -22467,7 +22467,7 @@
     </row>
     <row r="603" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B603" t="s">
         <v>2317</v>
@@ -22490,7 +22490,7 @@
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B604" t="s">
         <v>2322</v>
@@ -22513,7 +22513,7 @@
     </row>
     <row r="605" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B605" t="s">
         <v>2327</v>
@@ -22536,7 +22536,7 @@
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B606" t="s">
         <v>2332</v>
@@ -22559,7 +22559,7 @@
     </row>
     <row r="607" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B607" t="s">
         <v>2337</v>
@@ -22582,7 +22582,7 @@
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B608" t="s">
         <v>2342</v>
@@ -22605,7 +22605,7 @@
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B609" t="s">
         <v>2347</v>
@@ -22628,7 +22628,7 @@
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B610" t="s">
         <v>2352</v>
@@ -22651,7 +22651,7 @@
     </row>
     <row r="611" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B611" t="s">
         <v>2357</v>
@@ -22674,7 +22674,7 @@
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B612" t="s">
         <v>2362</v>
@@ -22697,7 +22697,7 @@
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B613" t="s">
         <v>2367</v>
@@ -22720,7 +22720,7 @@
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B614" t="s">
         <v>2372</v>
@@ -22743,7 +22743,7 @@
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B615" t="s">
         <v>2377</v>
@@ -22766,7 +22766,7 @@
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B616" t="s">
         <v>2382</v>
@@ -22789,7 +22789,7 @@
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B617" t="s">
         <v>2387</v>
@@ -22812,7 +22812,7 @@
     </row>
     <row r="618" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B618" t="s">
         <v>2392</v>
@@ -22835,7 +22835,7 @@
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B619" t="s">
         <v>2397</v>
@@ -22858,7 +22858,7 @@
     </row>
     <row r="620" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B620" t="s">
         <v>2402</v>
@@ -22881,7 +22881,7 @@
     </row>
     <row r="621" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B621" t="s">
         <v>2407</v>
@@ -22904,7 +22904,7 @@
     </row>
     <row r="622" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B622" t="s">
         <v>2412</v>
@@ -22927,7 +22927,7 @@
     </row>
     <row r="623" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B623" t="s">
         <v>2417</v>
@@ -22950,7 +22950,7 @@
     </row>
     <row r="624" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B624" t="s">
         <v>2422</v>
@@ -22973,7 +22973,7 @@
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B625" t="s">
         <v>2427</v>
@@ -22996,7 +22996,7 @@
     </row>
     <row r="626" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B626" t="s">
         <v>2431</v>
@@ -23019,7 +23019,7 @@
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B627" t="s">
         <v>2436</v>
@@ -23042,7 +23042,7 @@
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B628" t="s">
         <v>2441</v>
@@ -23065,7 +23065,7 @@
     </row>
     <row r="629" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B629" t="s">
         <v>2446</v>
@@ -23088,7 +23088,7 @@
     </row>
     <row r="630" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B630" t="s">
         <v>2451</v>
@@ -23111,7 +23111,7 @@
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B631" t="s">
         <v>2456</v>
@@ -23134,7 +23134,7 @@
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B632" t="s">
         <v>2461</v>
@@ -23157,7 +23157,7 @@
     </row>
     <row r="633" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B633" t="s">
         <v>2466</v>
@@ -23180,7 +23180,7 @@
     </row>
     <row r="634" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B634" t="s">
         <v>2471</v>
@@ -23203,7 +23203,7 @@
     </row>
     <row r="635" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B635" t="s">
         <v>2476</v>
@@ -23226,7 +23226,7 @@
     </row>
     <row r="636" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B636" t="s">
         <v>2481</v>
@@ -23249,7 +23249,7 @@
     </row>
     <row r="637" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B637" t="s">
         <v>2486</v>
@@ -23272,7 +23272,7 @@
     </row>
     <row r="638" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B638" t="s">
         <v>2491</v>
@@ -23295,7 +23295,7 @@
     </row>
     <row r="639" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B639" t="s">
         <v>2496</v>
@@ -23318,7 +23318,7 @@
     </row>
     <row r="640" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B640" t="s">
         <v>2501</v>
@@ -23341,7 +23341,7 @@
     </row>
     <row r="641" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B641" t="s">
         <v>2506</v>
@@ -23364,7 +23364,7 @@
     </row>
     <row r="642" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B642" t="s">
         <v>2511</v>
@@ -23387,7 +23387,7 @@
     </row>
     <row r="643" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B643" t="s">
         <v>2516</v>
@@ -23410,7 +23410,7 @@
     </row>
     <row r="644" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B644" t="s">
         <v>2521</v>
@@ -23433,7 +23433,7 @@
     </row>
     <row r="645" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B645" t="s">
         <v>2526</v>
@@ -23456,7 +23456,7 @@
     </row>
     <row r="646" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B646" t="s">
         <v>2531</v>
@@ -23479,7 +23479,7 @@
     </row>
     <row r="647" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B647" t="s">
         <v>2536</v>
@@ -23502,7 +23502,7 @@
     </row>
     <row r="648" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B648" t="s">
         <v>2541</v>
@@ -23525,7 +23525,7 @@
     </row>
     <row r="649" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B649" t="s">
         <v>2546</v>
@@ -23548,7 +23548,7 @@
     </row>
     <row r="650" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B650" t="s">
         <v>2551</v>
@@ -23571,7 +23571,7 @@
     </row>
     <row r="651" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B651" t="s">
         <v>2555</v>
@@ -23594,7 +23594,7 @@
     </row>
     <row r="652" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B652" t="s">
         <v>2560</v>
@@ -23617,7 +23617,7 @@
     </row>
     <row r="653" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B653" t="s">
         <v>2565</v>
@@ -23640,7 +23640,7 @@
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B654" t="s">
         <v>2570</v>
@@ -23663,7 +23663,7 @@
     </row>
     <row r="655" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B655" t="s">
         <v>2575</v>
@@ -23686,7 +23686,7 @@
     </row>
     <row r="656" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B656" t="s">
         <v>2580</v>
@@ -23709,7 +23709,7 @@
     </row>
     <row r="657" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B657" t="s">
         <v>2585</v>
@@ -23726,7 +23726,7 @@
     </row>
     <row r="658" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B658" t="s">
         <v>2588</v>
@@ -23749,7 +23749,7 @@
     </row>
     <row r="659" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B659" t="s">
         <v>2592</v>
@@ -23772,7 +23772,7 @@
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B660" t="s">
         <v>2597</v>
@@ -23795,7 +23795,7 @@
     </row>
     <row r="661" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B661" t="s">
         <v>2602</v>
@@ -23812,7 +23812,7 @@
     </row>
     <row r="662" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B662" t="s">
         <v>2605</v>
@@ -23835,7 +23835,7 @@
     </row>
     <row r="663" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B663" t="s">
         <v>2609</v>
@@ -23858,7 +23858,7 @@
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B664" t="s">
         <v>2614</v>
@@ -23881,7 +23881,7 @@
     </row>
     <row r="665" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B665" t="s">
         <v>2619</v>
@@ -23904,7 +23904,7 @@
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B666" t="s">
         <v>2623</v>
@@ -23921,7 +23921,7 @@
     </row>
     <row r="667" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B667" t="s">
         <v>2626</v>
@@ -23938,7 +23938,7 @@
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B668" t="s">
         <v>2629</v>
@@ -23961,7 +23961,7 @@
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B669" t="s">
         <v>2634</v>
@@ -23984,7 +23984,7 @@
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B670" t="s">
         <v>2639</v>
@@ -24001,7 +24001,7 @@
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B671" t="s">
         <v>2642</v>
@@ -24018,7 +24018,7 @@
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="B672" t="s">
         <v>2644</v>
@@ -24035,7 +24035,7 @@
     </row>
     <row r="673" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="B673" t="s">
         <v>2647</v>
@@ -24052,7 +24052,7 @@
     </row>
     <row r="674" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="B674" t="s">
         <v>2650</v>
@@ -24069,7 +24069,7 @@
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="B675" t="s">
         <v>1726</v>
@@ -24086,7 +24086,7 @@
     </row>
     <row r="676" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B676" t="s">
         <v>2653</v>
@@ -24103,7 +24103,7 @@
     </row>
     <row r="677" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B677" t="s">
         <v>2656</v>
@@ -24120,7 +24120,7 @@
     </row>
     <row r="678" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B678" t="s">
         <v>2659</v>
@@ -24137,7 +24137,7 @@
     </row>
     <row r="679" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B679" t="s">
         <v>2662</v>
@@ -24154,7 +24154,7 @@
     </row>
     <row r="680" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B680" t="s">
         <v>2664</v>
@@ -24171,7 +24171,7 @@
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B681" t="s">
         <v>2667</v>
@@ -24188,7 +24188,7 @@
     </row>
     <row r="682" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B682" t="s">
         <v>2670</v>
@@ -24211,7 +24211,7 @@
     </row>
     <row r="683" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B683" t="s">
         <v>2675</v>
@@ -24228,7 +24228,7 @@
     </row>
     <row r="684" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B684" t="s">
         <v>2678</v>
@@ -24245,7 +24245,7 @@
     </row>
     <row r="685" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="B685" t="s">
         <v>2681</v>
@@ -24268,7 +24268,7 @@
     </row>
     <row r="686" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="B686" t="s">
         <v>2686</v>
@@ -24291,7 +24291,7 @@
     </row>
     <row r="687" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="B687" t="s">
         <v>2691</v>
@@ -24308,7 +24308,7 @@
     </row>
     <row r="688" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="B688" t="s">
         <v>2694</v>
@@ -24325,7 +24325,7 @@
     </row>
     <row r="689" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="B689" t="s">
         <v>2697</v>
@@ -24342,7 +24342,7 @@
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="B690" t="s">
         <v>2700</v>
@@ -24359,7 +24359,7 @@
     </row>
     <row r="691" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="B691" t="s">
         <v>2703</v>
@@ -24382,7 +24382,7 @@
     </row>
     <row r="692" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B692" t="s">
         <v>2708</v>
@@ -24405,7 +24405,7 @@
     </row>
     <row r="693" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B693" t="s">
         <v>2713</v>
@@ -24428,7 +24428,7 @@
     </row>
     <row r="694" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B694" t="s">
         <v>2718</v>
@@ -24451,7 +24451,7 @@
     </row>
     <row r="695" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B695" t="s">
         <v>2723</v>
@@ -24468,7 +24468,7 @@
     </row>
     <row r="696" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B696" t="s">
         <v>2724</v>
@@ -24491,7 +24491,7 @@
     </row>
     <row r="697" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B697" t="s">
         <v>2729</v>
@@ -24508,7 +24508,7 @@
     </row>
     <row r="698" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B698" t="s">
         <v>2732</v>
@@ -24525,7 +24525,7 @@
     </row>
     <row r="699" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B699" t="s">
         <v>2735</v>
@@ -24542,7 +24542,7 @@
     </row>
     <row r="700" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B700" t="s">
         <v>2738</v>
@@ -24565,7 +24565,7 @@
     </row>
     <row r="701" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B701" t="s">
         <v>2742</v>
@@ -24582,7 +24582,7 @@
     </row>
     <row r="702" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B702" t="s">
         <v>2745</v>
@@ -24605,7 +24605,7 @@
     </row>
     <row r="703" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B703" t="s">
         <v>2750</v>
@@ -24628,7 +24628,7 @@
     </row>
     <row r="704" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B704" t="s">
         <v>2755</v>
@@ -24651,7 +24651,7 @@
     </row>
     <row r="705" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B705" t="s">
         <v>2760</v>
@@ -24674,7 +24674,7 @@
     </row>
     <row r="706" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B706" t="s">
         <v>2765</v>
@@ -24697,7 +24697,7 @@
     </row>
     <row r="707" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B707" t="s">
         <v>2770</v>
@@ -24720,7 +24720,7 @@
     </row>
     <row r="708" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B708" t="s">
         <v>2775</v>
@@ -24743,7 +24743,7 @@
     </row>
     <row r="709" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B709" t="s">
         <v>2780</v>
@@ -24766,7 +24766,7 @@
     </row>
     <row r="710" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B710" t="s">
         <v>2784</v>
@@ -24789,7 +24789,7 @@
     </row>
     <row r="711" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B711" t="s">
         <v>2788</v>
@@ -24812,7 +24812,7 @@
     </row>
     <row r="712" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B712" t="s">
         <v>2793</v>
@@ -24835,7 +24835,7 @@
     </row>
     <row r="713" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B713" t="s">
         <v>2798</v>
@@ -24858,7 +24858,7 @@
     </row>
     <row r="714" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B714" t="s">
         <v>2803</v>
@@ -24881,7 +24881,7 @@
     </row>
     <row r="715" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B715" t="s">
         <v>2808</v>
@@ -24904,7 +24904,7 @@
     </row>
     <row r="716" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B716" t="s">
         <v>2813</v>
@@ -24921,7 +24921,7 @@
     </row>
     <row r="717" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B717" t="s">
         <v>2816</v>
@@ -24944,7 +24944,7 @@
     </row>
     <row r="718" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B718" t="s">
         <v>2820</v>
@@ -24961,7 +24961,7 @@
     </row>
     <row r="719" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B719" t="s">
         <v>2823</v>
@@ -24978,7 +24978,7 @@
     </row>
     <row r="720" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B720" t="s">
         <v>2826</v>
@@ -24995,7 +24995,7 @@
     </row>
     <row r="721" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B721" t="s">
         <v>2829</v>
@@ -25012,7 +25012,7 @@
     </row>
     <row r="722" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B722" t="s">
         <v>2832</v>
@@ -25029,7 +25029,7 @@
     </row>
     <row r="723" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B723" t="s">
         <v>2835</v>
@@ -25052,7 +25052,7 @@
     </row>
     <row r="724" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B724" t="s">
         <v>2839</v>
@@ -25069,7 +25069,7 @@
     </row>
     <row r="725" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B725" t="s">
         <v>2842</v>
@@ -25086,7 +25086,7 @@
     </row>
     <row r="726" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B726" t="s">
         <v>2845</v>
@@ -25103,7 +25103,7 @@
     </row>
     <row r="727" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B727" t="s">
         <v>2847</v>
@@ -25120,7 +25120,7 @@
     </row>
     <row r="728" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B728" t="s">
         <v>2849</v>
@@ -25137,7 +25137,7 @@
     </row>
     <row r="729" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B729" t="s">
         <v>2852</v>
@@ -25154,7 +25154,7 @@
     </row>
     <row r="730" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B730" t="s">
         <v>2855</v>
@@ -25171,7 +25171,7 @@
     </row>
     <row r="731" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B731" t="s">
         <v>2857</v>
@@ -25188,7 +25188,7 @@
     </row>
     <row r="732" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B732" t="s">
         <v>2860</v>
@@ -25205,7 +25205,7 @@
     </row>
     <row r="733" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B733" t="s">
         <v>2863</v>
@@ -25222,7 +25222,7 @@
     </row>
     <row r="734" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B734" t="s">
         <v>2735</v>
@@ -25239,7 +25239,7 @@
     </row>
     <row r="735" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B735" t="s">
         <v>2867</v>
@@ -25256,7 +25256,7 @@
     </row>
     <row r="736" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B736" t="s">
         <v>2868</v>
@@ -25273,7 +25273,7 @@
     </row>
     <row r="737" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B737" t="s">
         <v>2871</v>
@@ -25290,7 +25290,7 @@
     </row>
     <row r="738" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B738" t="s">
         <v>2874</v>
@@ -25307,7 +25307,7 @@
     </row>
     <row r="739" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B739" t="s">
         <v>2877</v>
@@ -25324,7 +25324,7 @@
     </row>
     <row r="740" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B740" t="s">
         <v>2880</v>
@@ -25341,7 +25341,7 @@
     </row>
     <row r="741" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B741" t="s">
         <v>2883</v>
@@ -25364,7 +25364,7 @@
     </row>
     <row r="742" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B742" t="s">
         <v>2887</v>
@@ -25387,7 +25387,7 @@
     </row>
     <row r="743" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B743" t="s">
         <v>2892</v>
@@ -25410,7 +25410,7 @@
     </row>
     <row r="744" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B744" t="s">
         <v>2897</v>
@@ -25433,7 +25433,7 @@
     </row>
     <row r="745" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B745" t="s">
         <v>2902</v>
@@ -25450,7 +25450,7 @@
     </row>
     <row r="746" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B746" t="s">
         <v>2904</v>
@@ -25467,7 +25467,7 @@
     </row>
     <row r="747" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B747" t="s">
         <v>2907</v>
@@ -25484,7 +25484,7 @@
     </row>
     <row r="748" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B748" t="s">
         <v>2910</v>
@@ -25501,7 +25501,7 @@
     </row>
     <row r="749" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B749" t="s">
         <v>2913</v>
@@ -25518,7 +25518,7 @@
     </row>
     <row r="750" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B750" t="s">
         <v>2916</v>
@@ -25535,7 +25535,7 @@
     </row>
     <row r="751" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B751" t="s">
         <v>2919</v>
@@ -25552,7 +25552,7 @@
     </row>
     <row r="752" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B752" t="s">
         <v>2922</v>
@@ -25575,7 +25575,7 @@
     </row>
     <row r="753" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B753" t="s">
         <v>2927</v>
@@ -25598,7 +25598,7 @@
     </row>
     <row r="754" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B754" t="s">
         <v>2932</v>
@@ -25615,7 +25615,7 @@
     </row>
     <row r="755" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B755" t="s">
         <v>2935</v>
@@ -25632,7 +25632,7 @@
     </row>
     <row r="756" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B756" t="s">
         <v>2938</v>
@@ -25649,7 +25649,7 @@
     </row>
     <row r="757" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B757" t="s">
         <v>2940</v>
@@ -25666,7 +25666,7 @@
     </row>
     <row r="758" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B758" t="s">
         <v>2943</v>
@@ -25689,7 +25689,7 @@
     </row>
     <row r="759" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B759" t="s">
         <v>2948</v>
@@ -25712,7 +25712,7 @@
     </row>
     <row r="760" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B760" t="s">
         <v>2953</v>
@@ -25729,13 +25729,13 @@
     </row>
     <row r="761" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B761" t="s">
         <v>2956</v>
       </c>
       <c r="C761" s="4" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
       <c r="D761" s="4" t="s">
         <v>2957</v>
@@ -25746,7 +25746,7 @@
     </row>
     <row r="762" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B762" t="s">
         <v>2958</v>
@@ -25763,7 +25763,7 @@
     </row>
     <row r="763" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="B763" t="s">
         <v>2961</v>
@@ -25780,7 +25780,7 @@
     </row>
     <row r="764" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="B764" t="s">
         <v>2964</v>
@@ -25797,7 +25797,7 @@
     </row>
     <row r="765" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="B765" t="s">
         <v>2967</v>
@@ -25820,7 +25820,7 @@
     </row>
     <row r="766" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B766" t="s">
         <v>2972</v>
@@ -25840,7 +25840,7 @@
     </row>
     <row r="767" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B767" t="s">
         <v>2976</v>
@@ -25863,7 +25863,7 @@
     </row>
     <row r="768" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B768" t="s">
         <v>2981</v>
@@ -25886,7 +25886,7 @@
     </row>
     <row r="769" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B769" t="s">
         <v>2984</v>
@@ -25909,7 +25909,7 @@
     </row>
     <row r="770" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B770" t="s">
         <v>2989</v>
@@ -25932,7 +25932,7 @@
     </row>
     <row r="771" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A771" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="B771" t="s">
         <v>2994</v>
@@ -25955,7 +25955,7 @@
     </row>
     <row r="772" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="B772" t="s">
         <v>2999</v>
@@ -25978,7 +25978,7 @@
     </row>
     <row r="773" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B773" t="s">
         <v>3004</v>
@@ -26001,7 +26001,7 @@
     </row>
     <row r="774" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A774" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B774" t="s">
         <v>3009</v>
@@ -26024,7 +26024,7 @@
     </row>
     <row r="775" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A775" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B775" t="s">
         <v>3014</v>
@@ -26047,7 +26047,7 @@
     </row>
     <row r="776" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A776" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B776" t="s">
         <v>3019</v>
@@ -26090,7 +26090,7 @@
     </row>
     <row r="778" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A778" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B778" t="s">
         <v>3028</v>
@@ -26113,7 +26113,7 @@
     </row>
     <row r="779" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A779" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B779" t="s">
         <v>3033</v>
@@ -26136,7 +26136,7 @@
     </row>
     <row r="780" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A780" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B780" t="s">
         <v>3038</v>
@@ -26159,7 +26159,7 @@
     </row>
     <row r="781" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A781" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B781" t="s">
         <v>3043</v>
@@ -26182,7 +26182,7 @@
     </row>
     <row r="782" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A782" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B782" t="s">
         <v>3048</v>
@@ -26205,7 +26205,7 @@
     </row>
     <row r="783" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A783" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B783" t="s">
         <v>3053</v>
@@ -26228,7 +26228,7 @@
     </row>
     <row r="784" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A784" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B784" t="s">
         <v>3058</v>
@@ -26251,7 +26251,7 @@
     </row>
     <row r="785" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A785" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B785" t="s">
         <v>3063</v>
@@ -26294,7 +26294,7 @@
     </row>
     <row r="787" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A787" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B787" t="s">
         <v>3072</v>
@@ -26317,7 +26317,7 @@
     </row>
     <row r="788" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A788" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="B788" t="s">
         <v>2694</v>
@@ -26340,22 +26340,22 @@
     </row>
     <row r="789" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A789" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B789" t="s">
         <v>3080</v>
       </c>
       <c r="C789" s="4" t="s">
+        <v>3129</v>
+      </c>
+      <c r="D789" s="4" t="s">
         <v>3081</v>
       </c>
-      <c r="D789" s="4" t="s">
+      <c r="E789" s="5" t="s">
         <v>3082</v>
       </c>
-      <c r="E789" s="5" t="s">
+      <c r="F789" s="4" t="s">
         <v>3083</v>
-      </c>
-      <c r="F789" s="4" t="s">
-        <v>3084</v>
       </c>
       <c r="G789">
         <v>1</v>
@@ -26363,22 +26363,22 @@
     </row>
     <row r="790" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A790" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B790" t="s">
+        <v>3084</v>
+      </c>
+      <c r="C790" s="4" t="s">
         <v>3085</v>
       </c>
-      <c r="C790" s="4" t="s">
+      <c r="D790" s="4" t="s">
         <v>3086</v>
       </c>
-      <c r="D790" s="4" t="s">
+      <c r="E790" s="5" t="s">
         <v>3087</v>
       </c>
-      <c r="E790" s="5" t="s">
+      <c r="F790" s="4" t="s">
         <v>3088</v>
-      </c>
-      <c r="F790" s="4" t="s">
-        <v>3089</v>
       </c>
       <c r="G790">
         <v>1</v>
@@ -26386,16 +26386,16 @@
     </row>
     <row r="791" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A791" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="B791" t="s">
+        <v>3089</v>
+      </c>
+      <c r="C791" s="4" t="s">
         <v>3090</v>
       </c>
-      <c r="C791" s="4" t="s">
+      <c r="D791" s="4" t="s">
         <v>3091</v>
-      </c>
-      <c r="D791" s="4" t="s">
-        <v>3092</v>
       </c>
       <c r="G791">
         <v>0</v>
@@ -26403,22 +26403,22 @@
     </row>
     <row r="792" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A792" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B792" t="s">
+        <v>3092</v>
+      </c>
+      <c r="C792" s="4" t="s">
         <v>3093</v>
       </c>
-      <c r="C792" s="4" t="s">
+      <c r="D792" s="4" t="s">
         <v>3094</v>
       </c>
-      <c r="D792" s="4" t="s">
+      <c r="E792" s="5" t="s">
         <v>3095</v>
       </c>
-      <c r="E792" s="5" t="s">
+      <c r="F792" s="4" t="s">
         <v>3096</v>
-      </c>
-      <c r="F792" s="4" t="s">
-        <v>3097</v>
       </c>
       <c r="G792">
         <v>1</v>
@@ -26426,22 +26426,22 @@
     </row>
     <row r="793" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A793" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B793" t="s">
         <v>2808</v>
       </c>
       <c r="C793" s="4" t="s">
+        <v>3097</v>
+      </c>
+      <c r="D793" s="4" t="s">
         <v>3098</v>
       </c>
-      <c r="D793" s="4" t="s">
+      <c r="E793" s="5" t="s">
         <v>3099</v>
       </c>
-      <c r="E793" s="5" t="s">
+      <c r="F793" s="4" t="s">
         <v>3100</v>
-      </c>
-      <c r="F793" s="4" t="s">
-        <v>3101</v>
       </c>
       <c r="G793">
         <v>1</v>
@@ -26449,19 +26449,19 @@
     </row>
     <row r="794" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A794" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B794" t="s">
+        <v>3101</v>
+      </c>
+      <c r="C794" s="4" t="s">
         <v>3102</v>
-      </c>
-      <c r="C794" s="4" t="s">
-        <v>3103</v>
       </c>
       <c r="D794" s="4" t="s">
         <v>2553</v>
       </c>
       <c r="E794" s="5" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
     </row>
   </sheetData>
